--- a/IA_CCBS_BANK_SIDE/RepaymentSchedule/RepaymentSchedule_Save.xlsx
+++ b/IA_CCBS_BANK_SIDE/RepaymentSchedule/RepaymentSchedule_Save.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20400"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sw\Relational_Files\Interfaces Repayment Schedule\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sw\Relational_Files\iApply\Interfaces\Interfaces_plus_allbanks\IA_CCBS_BANK_SIDE\RepaymentSchedule\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{293E0528-4C9D-48AA-9230-C88B8BCF2BB8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B7E3506-091F-416E-8303-DA40B1329B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-7800" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{CDB5EBE5-199B-4C02-A0AD-2F7510F763F7}"/>
+    <workbookView xWindow="28680" yWindow="-5550" windowWidth="30960" windowHeight="16920" xr2:uid="{CDB5EBE5-199B-4C02-A0AD-2F7510F763F7}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="3" r:id="rId1"/>
@@ -650,7 +650,7 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -733,22 +733,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -757,7 +748,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -767,6 +758,36 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="21">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -919,36 +940,6 @@
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -963,41 +954,41 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8E993AA3-9D86-4B54-B758-1BF06627D0F0}" name="Table3" displayName="Table3" ref="B2:H69" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8E993AA3-9D86-4B54-B758-1BF06627D0F0}" name="Table3" displayName="Table3" ref="B2:H69" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <autoFilter ref="B2:H69" xr:uid="{8E993AA3-9D86-4B54-B758-1BF06627D0F0}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{1D79BAF6-5220-4AB5-AE55-96590B0B07C7}" name="Seq." dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{5C08AD72-5937-43C3-8164-8A91093450D6}" name="Description" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{58FC589B-1CB4-441B-8A55-98FAE314A6F4}" name="Model" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{72055F84-5407-413A-BA6F-F5957E4899D7}" name="iApply" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{11310D34-1A8F-4B2D-9901-4922C5974E0C}" name="Data Type" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{490C6BB8-E0C1-46E5-90D1-F4711249B549}" name="Entities" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{25E23557-7236-4765-B171-BBF627A5F855}" name="Notes" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{1D79BAF6-5220-4AB5-AE55-96590B0B07C7}" name="Seq." dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{5C08AD72-5937-43C3-8164-8A91093450D6}" name="Description" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{58FC589B-1CB4-441B-8A55-98FAE314A6F4}" name="Model" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{72055F84-5407-413A-BA6F-F5957E4899D7}" name="iApply" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{11310D34-1A8F-4B2D-9901-4922C5974E0C}" name="Data Type" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{490C6BB8-E0C1-46E5-90D1-F4711249B549}" name="Entities" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{25E23557-7236-4765-B171-BBF627A5F855}" name="Notes" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{95AD6B62-2DA8-4727-83F6-7DF7747476EB}" name="Table4" displayName="Table4" ref="B2:H5" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{95AD6B62-2DA8-4727-83F6-7DF7747476EB}" name="Table4" displayName="Table4" ref="B2:H5" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="B2:H5" xr:uid="{95AD6B62-2DA8-4727-83F6-7DF7747476EB}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{413F1299-0565-47BB-B0AB-4F739703DB66}" name="Seq." dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{3BCF002E-AC39-4B19-9001-C00719682CFC}" name="Description" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{50BB9506-611A-4107-B63F-3441DF5CC4F7}" name="Model" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{60E06B8F-4894-477B-93F9-FEB6DF9BE600}" name="iApply" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{ADC0EA44-7DAF-43BB-B614-9EFA90B330CE}" name="Data Type" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{2C1C0F9E-F29A-4534-AD4A-90BA93A067D2}" name="Entities" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{D68DF882-D84B-494D-B1BB-C1EE9D02B239}" name="Notes" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{413F1299-0565-47BB-B0AB-4F739703DB66}" name="Seq." dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{3BCF002E-AC39-4B19-9001-C00719682CFC}" name="Description" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{50BB9506-611A-4107-B63F-3441DF5CC4F7}" name="Model" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{60E06B8F-4894-477B-93F9-FEB6DF9BE600}" name="iApply" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{ADC0EA44-7DAF-43BB-B614-9EFA90B330CE}" name="Data Type" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{2C1C0F9E-F29A-4534-AD4A-90BA93A067D2}" name="Entities" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{D68DF882-D84B-494D-B1BB-C1EE9D02B239}" name="Notes" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1035,7 +1026,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1141,7 +1132,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1283,7 +1274,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1317,7 +1308,7 @@
       <c r="B4" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="31" t="s">
         <v>151</v>
       </c>
     </row>
@@ -1333,7 +1324,7 @@
       <c r="B6" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="31" t="s">
         <v>147</v>
       </c>
     </row>
@@ -1363,7 +1354,7 @@
       <c r="B11" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" s="31" t="s">
         <v>150</v>
       </c>
     </row>
@@ -1427,7 +1418,7 @@
       <c r="F2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="35" t="s">
+      <c r="G2" s="32" t="s">
         <v>155</v>
       </c>
       <c r="H2" s="19" t="s">
@@ -1438,178 +1429,178 @@
       <c r="B3" s="28">
         <v>1</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29" t="s">
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29" t="s">
+      <c r="F3" s="6"/>
+      <c r="G3" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="H3" s="36"/>
+      <c r="H3" s="33"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="28">
         <v>2</v>
       </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29" t="s">
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F4" s="30"/>
-      <c r="G4" s="29" t="s">
+      <c r="F4" s="29"/>
+      <c r="G4" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="H4" s="36"/>
+      <c r="H4" s="33"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="28">
         <v>3</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29" t="s">
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="30"/>
-      <c r="G5" s="29" t="s">
+      <c r="F5" s="29"/>
+      <c r="G5" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="H5" s="36"/>
+      <c r="H5" s="33"/>
     </row>
     <row r="6" spans="2:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="28">
         <v>4</v>
       </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29" t="s">
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29" t="s">
+      <c r="F6" s="6"/>
+      <c r="G6" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="H6" s="36"/>
+      <c r="H6" s="33"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="28">
         <v>5</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29" t="s">
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29" t="s">
+      <c r="F7" s="6"/>
+      <c r="G7" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="H7" s="36"/>
+      <c r="H7" s="33"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" s="28">
         <v>6</v>
       </c>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29" t="s">
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29" t="s">
+      <c r="F8" s="6"/>
+      <c r="G8" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="H8" s="36"/>
+      <c r="H8" s="33"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="28">
         <v>7</v>
       </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29" t="s">
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29" t="s">
+      <c r="F9" s="6"/>
+      <c r="G9" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="H9" s="36"/>
+      <c r="H9" s="33"/>
     </row>
     <row r="10" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="28">
         <v>8</v>
       </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29" t="s">
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29" t="s">
+      <c r="F10" s="6"/>
+      <c r="G10" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="H10" s="36"/>
+      <c r="H10" s="33"/>
     </row>
     <row r="11" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="28">
         <v>9</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29" t="s">
+      <c r="D11" s="6"/>
+      <c r="E11" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H11" s="36"/>
+      <c r="F11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H11" s="33"/>
     </row>
     <row r="12" spans="2:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="28">
         <v>10</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29" t="s">
+      <c r="D12" s="6"/>
+      <c r="E12" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="30" t="s">
+      <c r="F12" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H12" s="36"/>
+      <c r="G12" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H12" s="33"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="28">
         <v>11</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29" t="s">
+      <c r="D13" s="6"/>
+      <c r="E13" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="29" t="s">
+      <c r="F13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H13" s="36" t="s">
+      <c r="G13" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H13" s="33" t="s">
         <v>154</v>
       </c>
     </row>
@@ -1617,512 +1608,512 @@
       <c r="B14" s="28">
         <v>12</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29" t="s">
+      <c r="D14" s="6"/>
+      <c r="E14" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="29" t="s">
+      <c r="F14" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G14" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H14" s="36"/>
+      <c r="G14" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H14" s="33"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="28">
         <v>13</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29" t="s">
+      <c r="D15" s="6"/>
+      <c r="E15" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F15" s="29" t="s">
+      <c r="F15" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G15" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H15" s="36"/>
+      <c r="G15" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H15" s="33"/>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="28">
         <v>14</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29" t="s">
+      <c r="D16" s="6"/>
+      <c r="E16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H16" s="36"/>
+      <c r="F16" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H16" s="33"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="28">
         <v>15</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29" t="s">
+      <c r="D17" s="6"/>
+      <c r="E17" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="29" t="s">
+      <c r="F17" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="G17" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H17" s="36"/>
+      <c r="G17" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H17" s="33"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="28">
         <v>16</v>
       </c>
-      <c r="C18" s="31" t="s">
+      <c r="C18" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="31"/>
-      <c r="E18" s="29" t="s">
+      <c r="D18" s="5"/>
+      <c r="E18" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F18" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H18" s="36"/>
+      <c r="F18" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H18" s="33"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="28">
         <v>17</v>
       </c>
-      <c r="C19" s="31" t="s">
+      <c r="C19" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="31"/>
-      <c r="E19" s="29" t="s">
+      <c r="D19" s="5"/>
+      <c r="E19" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F19" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H19" s="36"/>
+      <c r="F19" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H19" s="33"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="28">
         <v>18</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C20" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="31"/>
-      <c r="E20" s="29" t="s">
+      <c r="D20" s="5"/>
+      <c r="E20" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F20" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H20" s="36"/>
+      <c r="F20" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H20" s="33"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="28">
         <v>19</v>
       </c>
-      <c r="C21" s="31" t="s">
+      <c r="C21" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="31"/>
-      <c r="E21" s="29" t="s">
+      <c r="D21" s="5"/>
+      <c r="E21" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F21" s="29" t="s">
+      <c r="F21" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G21" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H21" s="36"/>
+      <c r="G21" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H21" s="33"/>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="28">
         <v>20</v>
       </c>
-      <c r="C22" s="31" t="s">
+      <c r="C22" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D22" s="31"/>
-      <c r="E22" s="29" t="s">
+      <c r="D22" s="5"/>
+      <c r="E22" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F22" s="29" t="s">
+      <c r="F22" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G22" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H22" s="36"/>
+      <c r="G22" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H22" s="33"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="28">
         <v>21</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29" t="s">
+      <c r="D23" s="6"/>
+      <c r="E23" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F23" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H23" s="36"/>
+      <c r="F23" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H23" s="33"/>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="28">
         <v>22</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29" t="s">
+      <c r="D24" s="6"/>
+      <c r="E24" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F24" s="29" t="s">
+      <c r="F24" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G24" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H24" s="36"/>
+      <c r="G24" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H24" s="33"/>
     </row>
     <row r="25" spans="2:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="28">
         <v>23</v>
       </c>
-      <c r="C25" s="31" t="s">
+      <c r="C25" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D25" s="31"/>
-      <c r="E25" s="29" t="s">
+      <c r="D25" s="5"/>
+      <c r="E25" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="F25" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H25" s="36"/>
+      <c r="F25" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H25" s="33"/>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="28">
         <v>24</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29" t="s">
+      <c r="D26" s="6"/>
+      <c r="E26" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F26" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="G26" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H26" s="36"/>
+      <c r="F26" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H26" s="33"/>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="28">
         <v>25</v>
       </c>
-      <c r="C27" s="31" t="s">
+      <c r="C27" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D27" s="31"/>
-      <c r="E27" s="29" t="s">
+      <c r="D27" s="5"/>
+      <c r="E27" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F27" s="29" t="s">
+      <c r="F27" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="G27" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H27" s="36"/>
+      <c r="G27" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H27" s="33"/>
     </row>
     <row r="28" spans="2:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="28">
         <v>26</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29" t="s">
+      <c r="D28" s="6"/>
+      <c r="E28" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="F28" s="29" t="s">
+      <c r="F28" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="G28" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H28" s="36"/>
+      <c r="G28" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H28" s="33"/>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="28">
         <v>27</v>
       </c>
-      <c r="C29" s="31" t="s">
+      <c r="C29" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D29" s="31"/>
-      <c r="E29" s="29" t="s">
+      <c r="D29" s="5"/>
+      <c r="E29" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="F29" s="29" t="s">
+      <c r="F29" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="G29" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H29" s="36"/>
+      <c r="G29" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H29" s="33"/>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="28">
         <v>28</v>
       </c>
-      <c r="C30" s="31" t="s">
+      <c r="C30" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31" t="s">
+      <c r="D30" s="5"/>
+      <c r="E30" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F30" s="29" t="s">
+      <c r="F30" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="G30" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H30" s="36"/>
+      <c r="G30" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H30" s="33"/>
     </row>
     <row r="31" spans="2:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="28">
         <v>29</v>
       </c>
-      <c r="C31" s="29" t="s">
+      <c r="C31" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D31" s="29"/>
-      <c r="E31" s="31" t="s">
+      <c r="D31" s="6"/>
+      <c r="E31" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="F31" s="29" t="s">
+      <c r="F31" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="G31" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H31" s="36"/>
+      <c r="G31" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H31" s="33"/>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B32" s="28">
         <v>30</v>
       </c>
-      <c r="C32" s="31" t="s">
+      <c r="C32" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31" t="s">
+      <c r="D32" s="5"/>
+      <c r="E32" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="F32" s="29" t="s">
+      <c r="F32" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="G32" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H32" s="36"/>
+      <c r="G32" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H32" s="33"/>
     </row>
     <row r="33" spans="2:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="28">
         <v>31</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D33" s="29"/>
-      <c r="E33" s="31" t="s">
+      <c r="D33" s="6"/>
+      <c r="E33" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F33" s="31" t="s">
+      <c r="F33" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G33" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H33" s="36"/>
+      <c r="G33" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H33" s="33"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="28">
         <v>32</v>
       </c>
-      <c r="C34" s="31" t="s">
+      <c r="C34" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31" t="s">
+      <c r="D34" s="5"/>
+      <c r="E34" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="F34" s="29" t="s">
+      <c r="F34" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="G34" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H34" s="36"/>
+      <c r="G34" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H34" s="33"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="28">
         <v>33</v>
       </c>
-      <c r="C35" s="31" t="s">
+      <c r="C35" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31" t="s">
+      <c r="D35" s="5"/>
+      <c r="E35" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F35" s="29" t="s">
+      <c r="F35" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="G35" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H35" s="36"/>
+      <c r="G35" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H35" s="33"/>
     </row>
     <row r="36" spans="2:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="28">
         <v>34</v>
       </c>
-      <c r="C36" s="31" t="s">
+      <c r="C36" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31" t="s">
+      <c r="D36" s="5"/>
+      <c r="E36" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="F36" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G36" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H36" s="36"/>
+      <c r="F36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H36" s="33"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B37" s="28">
         <v>35</v>
       </c>
-      <c r="C37" s="31" t="s">
+      <c r="C37" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31" t="s">
+      <c r="D37" s="5"/>
+      <c r="E37" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="F37" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G37" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H37" s="36"/>
+      <c r="F37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H37" s="33"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B38" s="28">
         <v>36</v>
       </c>
-      <c r="C38" s="31" t="s">
+      <c r="C38" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="31"/>
-      <c r="E38" s="31" t="s">
+      <c r="D38" s="5"/>
+      <c r="E38" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="F38" s="31" t="s">
+      <c r="F38" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G38" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H38" s="36"/>
+      <c r="G38" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H38" s="33"/>
     </row>
     <row r="39" spans="2:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="28">
         <v>37</v>
       </c>
-      <c r="C39" s="31" t="s">
+      <c r="C39" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31" t="s">
+      <c r="D39" s="5"/>
+      <c r="E39" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="F39" s="31" t="s">
+      <c r="F39" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G39" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H39" s="36"/>
+      <c r="G39" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H39" s="33"/>
     </row>
     <row r="40" spans="2:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="28">
         <v>38</v>
       </c>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
-      <c r="E40" s="31" t="s">
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F40" s="31" t="s">
+      <c r="F40" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G40" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H40" s="36">
+      <c r="G40" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H40" s="33">
         <v>0</v>
       </c>
     </row>
@@ -2130,94 +2121,94 @@
       <c r="B41" s="28">
         <v>39</v>
       </c>
-      <c r="C41" s="31" t="s">
+      <c r="C41" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D41" s="31"/>
-      <c r="E41" s="31" t="s">
+      <c r="D41" s="5"/>
+      <c r="E41" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="F41" s="31" t="s">
+      <c r="F41" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G41" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H41" s="36"/>
+      <c r="G41" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H41" s="33"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B42" s="28">
         <v>40</v>
       </c>
-      <c r="C42" s="31" t="s">
+      <c r="C42" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="D42" s="31"/>
-      <c r="E42" s="31" t="s">
+      <c r="D42" s="5"/>
+      <c r="E42" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F42" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G42" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H42" s="36"/>
+      <c r="F42" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H42" s="33"/>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B43" s="28">
         <v>41</v>
       </c>
-      <c r="C43" s="31" t="s">
+      <c r="C43" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D43" s="31"/>
-      <c r="E43" s="31" t="s">
+      <c r="D43" s="5"/>
+      <c r="E43" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="F43" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G43" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H43" s="36"/>
+      <c r="F43" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H43" s="33"/>
     </row>
     <row r="44" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B44" s="28">
         <v>42</v>
       </c>
-      <c r="C44" s="31" t="s">
+      <c r="C44" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D44" s="31"/>
-      <c r="E44" s="31" t="s">
+      <c r="D44" s="5"/>
+      <c r="E44" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F44" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G44" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H44" s="36"/>
+      <c r="F44" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H44" s="33"/>
     </row>
     <row r="45" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B45" s="28">
         <v>43</v>
       </c>
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
-      <c r="E45" s="31" t="s">
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="F45" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G45" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H45" s="36">
+      <c r="F45" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H45" s="33">
         <v>0</v>
       </c>
     </row>
@@ -2225,18 +2216,18 @@
       <c r="B46" s="28">
         <v>44</v>
       </c>
-      <c r="C46" s="31"/>
-      <c r="D46" s="31"/>
-      <c r="E46" s="31" t="s">
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="F46" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G46" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H46" s="36">
+      <c r="F46" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H46" s="33">
         <v>0</v>
       </c>
     </row>
@@ -2244,18 +2235,18 @@
       <c r="B47" s="28">
         <v>45</v>
       </c>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31" t="s">
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F47" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G47" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H47" s="36">
+      <c r="F47" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H47" s="33">
         <v>1</v>
       </c>
     </row>
@@ -2263,18 +2254,18 @@
       <c r="B48" s="28">
         <v>46</v>
       </c>
-      <c r="C48" s="31"/>
-      <c r="D48" s="31"/>
-      <c r="E48" s="31" t="s">
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="F48" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G48" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H48" s="36">
+      <c r="F48" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H48" s="33">
         <v>0</v>
       </c>
     </row>
@@ -2282,132 +2273,132 @@
       <c r="B49" s="28">
         <v>47</v>
       </c>
-      <c r="C49" s="31" t="s">
+      <c r="C49" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="D49" s="31"/>
-      <c r="E49" s="31" t="s">
+      <c r="D49" s="5"/>
+      <c r="E49" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="F49" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G49" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H49" s="36"/>
+      <c r="F49" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H49" s="33"/>
     </row>
     <row r="50" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B50" s="28">
         <v>48</v>
       </c>
-      <c r="C50" s="31" t="s">
+      <c r="C50" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D50" s="31"/>
-      <c r="E50" s="31" t="s">
+      <c r="D50" s="5"/>
+      <c r="E50" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F50" s="31" t="s">
+      <c r="F50" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G50" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H50" s="36"/>
+      <c r="G50" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H50" s="33"/>
     </row>
     <row r="51" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B51" s="28">
         <v>49</v>
       </c>
-      <c r="C51" s="31" t="s">
+      <c r="C51" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D51" s="31"/>
-      <c r="E51" s="31" t="s">
+      <c r="D51" s="5"/>
+      <c r="E51" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="F51" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G51" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H51" s="36"/>
+      <c r="F51" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H51" s="33"/>
     </row>
     <row r="52" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B52" s="28">
         <v>50</v>
       </c>
-      <c r="C52" s="31" t="s">
+      <c r="C52" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="D52" s="31"/>
-      <c r="E52" s="31" t="s">
+      <c r="D52" s="5"/>
+      <c r="E52" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="F52" s="31" t="s">
+      <c r="F52" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G52" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H52" s="36"/>
+      <c r="G52" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H52" s="33"/>
     </row>
     <row r="53" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B53" s="28">
         <v>51</v>
       </c>
-      <c r="C53" s="31" t="s">
+      <c r="C53" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D53" s="31"/>
-      <c r="E53" s="31" t="s">
+      <c r="D53" s="5"/>
+      <c r="E53" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="F53" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G53" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H53" s="36"/>
+      <c r="F53" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H53" s="33"/>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B54" s="28">
         <v>52</v>
       </c>
-      <c r="C54" s="31" t="s">
+      <c r="C54" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="D54" s="31"/>
-      <c r="E54" s="31" t="s">
+      <c r="D54" s="5"/>
+      <c r="E54" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="F54" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G54" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H54" s="36"/>
+      <c r="F54" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H54" s="33"/>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B55" s="28">
         <v>53</v>
       </c>
-      <c r="C55" s="31"/>
-      <c r="D55" s="31"/>
-      <c r="E55" s="31" t="s">
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="F55" s="31" t="s">
+      <c r="F55" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G55" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H55" s="36">
+      <c r="G55" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H55" s="33">
         <v>0</v>
       </c>
     </row>
@@ -2415,18 +2406,18 @@
       <c r="B56" s="28">
         <v>54</v>
       </c>
-      <c r="C56" s="31"/>
-      <c r="D56" s="31"/>
-      <c r="E56" s="31" t="s">
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F56" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G56" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H56" s="36">
+      <c r="F56" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H56" s="33">
         <v>0</v>
       </c>
     </row>
@@ -2434,18 +2425,18 @@
       <c r="B57" s="28">
         <v>55</v>
       </c>
-      <c r="C57" s="31"/>
-      <c r="D57" s="31"/>
-      <c r="E57" s="31" t="s">
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="F57" s="31" t="s">
+      <c r="F57" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G57" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H57" s="36" t="s">
+      <c r="G57" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H57" s="33" t="s">
         <v>118</v>
       </c>
     </row>
@@ -2453,229 +2444,229 @@
       <c r="B58" s="28">
         <v>56</v>
       </c>
-      <c r="C58" s="31" t="s">
+      <c r="C58" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D58" s="31"/>
-      <c r="E58" s="31" t="s">
+      <c r="D58" s="5"/>
+      <c r="E58" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="F58" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G58" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H58" s="36"/>
+      <c r="F58" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H58" s="33"/>
     </row>
     <row r="59" spans="2:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B59" s="28">
         <v>57</v>
       </c>
-      <c r="C59" s="31" t="s">
+      <c r="C59" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="D59" s="31"/>
-      <c r="E59" s="31" t="s">
+      <c r="D59" s="5"/>
+      <c r="E59" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="F59" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G59" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H59" s="36"/>
+      <c r="F59" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H59" s="33"/>
     </row>
     <row r="60" spans="2:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B60" s="28">
         <v>58</v>
       </c>
-      <c r="C60" s="31" t="s">
+      <c r="C60" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D60" s="31"/>
-      <c r="E60" s="31" t="s">
+      <c r="D60" s="5"/>
+      <c r="E60" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="F60" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G60" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H60" s="36"/>
+      <c r="F60" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H60" s="33"/>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B61" s="28">
         <v>59</v>
       </c>
-      <c r="C61" s="31" t="s">
+      <c r="C61" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="D61" s="31"/>
-      <c r="E61" s="31" t="s">
+      <c r="D61" s="5"/>
+      <c r="E61" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="F61" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G61" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H61" s="36"/>
+      <c r="F61" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H61" s="33"/>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B62" s="28">
         <v>60</v>
       </c>
-      <c r="C62" s="31" t="s">
+      <c r="C62" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="D62" s="31"/>
-      <c r="E62" s="31" t="s">
+      <c r="D62" s="5"/>
+      <c r="E62" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="F62" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G62" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H62" s="36"/>
+      <c r="F62" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H62" s="33"/>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B63" s="28">
         <v>61</v>
       </c>
-      <c r="C63" s="31" t="s">
+      <c r="C63" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="D63" s="31"/>
-      <c r="E63" s="31" t="s">
+      <c r="D63" s="5"/>
+      <c r="E63" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="F63" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G63" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H63" s="36"/>
+      <c r="F63" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H63" s="33"/>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B64" s="28">
         <v>62</v>
       </c>
-      <c r="C64" s="31" t="s">
+      <c r="C64" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D64" s="31"/>
-      <c r="E64" s="31" t="s">
+      <c r="D64" s="5"/>
+      <c r="E64" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F64" s="31" t="s">
+      <c r="F64" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G64" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H64" s="36"/>
+      <c r="G64" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H64" s="33"/>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B65" s="28">
         <v>63</v>
       </c>
-      <c r="C65" s="31" t="s">
+      <c r="C65" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="D65" s="31"/>
-      <c r="E65" s="31" t="s">
+      <c r="D65" s="5"/>
+      <c r="E65" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="F65" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G65" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H65" s="36"/>
+      <c r="F65" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H65" s="33"/>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B66" s="28">
         <v>64</v>
       </c>
-      <c r="C66" s="31" t="s">
+      <c r="C66" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="D66" s="31"/>
-      <c r="E66" s="31" t="s">
+      <c r="D66" s="5"/>
+      <c r="E66" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="F66" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G66" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H66" s="36"/>
+      <c r="F66" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H66" s="33"/>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B67" s="28">
         <v>65</v>
       </c>
-      <c r="C67" s="31" t="s">
+      <c r="C67" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D67" s="31"/>
-      <c r="E67" s="31" t="s">
+      <c r="D67" s="5"/>
+      <c r="E67" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="F67" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G67" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H67" s="36"/>
+      <c r="F67" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H67" s="33"/>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B68" s="28">
         <v>66</v>
       </c>
-      <c r="C68" s="31" t="s">
+      <c r="C68" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="D68" s="31"/>
-      <c r="E68" s="31" t="s">
+      <c r="D68" s="5"/>
+      <c r="E68" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="F68" s="31" t="s">
+      <c r="F68" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="G68" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H68" s="36"/>
+      <c r="G68" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H68" s="33"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B69" s="28">
         <v>67</v>
       </c>
-      <c r="C69" s="31" t="s">
+      <c r="C69" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="D69" s="31"/>
-      <c r="E69" s="31" t="s">
+      <c r="D69" s="5"/>
+      <c r="E69" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="F69" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G69" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H69" s="36"/>
+      <c r="F69" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="H69" s="33"/>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B70" s="16"/>
@@ -3033,9 +3024,9 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="duplicateValues" dxfId="20" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -3081,61 +3072,61 @@
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="32">
+      <c r="B3" s="18">
         <v>1</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31" t="s">
+      <c r="D3" s="5"/>
+      <c r="E3" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="G3" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="H3" s="33"/>
+      <c r="H3" s="30"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="32">
+      <c r="B4" s="18">
         <v>2</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31" t="s">
+      <c r="D4" s="5"/>
+      <c r="E4" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="F4" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="31" t="s">
+      <c r="F4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="H4" s="33"/>
+      <c r="H4" s="30"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="32">
+      <c r="B5" s="18">
         <v>3</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31" t="s">
+      <c r="D5" s="5"/>
+      <c r="E5" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="F5" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="31" t="s">
+      <c r="F5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="H5" s="33"/>
+      <c r="H5" s="30"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
